--- a/artefacts/burndown-charts/burndown_chart.xlsx
+++ b/artefacts/burndown-charts/burndown_chart.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hiba9\safe-stay-ai\artefacts\burndown-charts\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5923539F-6A58-4E91-BF4C-47F59E627D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sprint 1 Burndown" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sprint 2 Burndown" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sprint 1 Burndown" sheetId="1" r:id="rId1"/>
+    <sheet name="Sprint 2 Burndown" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -23,90 +31,86 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
-    <t xml:space="preserve">Safe-Stay AI — Sprint 1 Burndown Chart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ideal Remaining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Remaining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safe-Stay AI — Sprint 2 Burndown Chart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 Apr</t>
+    <t>Safe-Stay AI — Sprint 1 Burndown Chart</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Ideal Remaining</t>
+  </si>
+  <si>
+    <t>Actual Remaining</t>
+  </si>
+  <si>
+    <t>1 Apr</t>
+  </si>
+  <si>
+    <t>2 Apr</t>
+  </si>
+  <si>
+    <t>3 Apr</t>
+  </si>
+  <si>
+    <t>4 Apr</t>
+  </si>
+  <si>
+    <t>5 Apr</t>
+  </si>
+  <si>
+    <t>6 Apr</t>
+  </si>
+  <si>
+    <t>7 Apr</t>
+  </si>
+  <si>
+    <t>8 Apr</t>
+  </si>
+  <si>
+    <t>9 Apr</t>
+  </si>
+  <si>
+    <t>Safe-Stay AI — Sprint 2 Burndown Chart</t>
+  </si>
+  <si>
+    <t>10 Apr</t>
+  </si>
+  <si>
+    <t>11 Apr</t>
+  </si>
+  <si>
+    <t>12 Apr</t>
+  </si>
+  <si>
+    <t>13 Apr</t>
+  </si>
+  <si>
+    <t>14 Apr</t>
+  </si>
+  <si>
+    <t>15 Apr</t>
+  </si>
+  <si>
+    <t>16 Apr</t>
+  </si>
+  <si>
+    <t>17 Apr</t>
+  </si>
+  <si>
+    <t>19 Apr</t>
+  </si>
+  <si>
+    <t>20 Apr</t>
+  </si>
+  <si>
+    <t>25 Apr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0"/>
-  </numFmts>
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,60 +119,22 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -192,14 +158,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
@@ -215,61 +181,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -328,15 +262,33 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF2E4057"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -345,7 +297,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -353,7 +305,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -374,6 +326,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -382,7 +335,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sprint 1 Burndown'!B3</c:f>
+              <c:f>'Sprint 1 Burndown'!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -392,12 +345,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ff6b35"/>
-            </a:solidFill>
             <a:ln w="20160">
               <a:solidFill>
-                <a:srgbClr val="ff6b35"/>
+                <a:srgbClr val="FF6B35"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -406,15 +356,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -422,8 +380,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -502,13 +461,18 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3F81-4E5F-944D-31861DE27997}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sprint 1 Burndown'!C3</c:f>
+              <c:f>'Sprint 1 Burndown'!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -518,12 +482,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="2e86ab"/>
-            </a:solidFill>
             <a:ln w="24840">
               <a:solidFill>
-                <a:srgbClr val="2e86ab"/>
+                <a:srgbClr val="2E86AB"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -532,15 +493,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -548,8 +517,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -628,7 +598,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3F81-4E5F-944D-31861DE27997}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -636,7 +619,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="50373887"/>
         <c:axId val="13584860"/>
       </c:lineChart>
@@ -654,7 +637,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -662,7 +645,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -698,13 +681,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="13584860"/>
@@ -740,7 +724,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -748,7 +732,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -784,13 +768,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="50373887"/>
@@ -818,37 +803,46 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -857,7 +851,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -865,7 +859,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -886,6 +880,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -894,7 +889,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sprint 2 Burndown'!B3</c:f>
+              <c:f>'Sprint 2 Burndown'!$B$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -904,12 +899,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="ff6b35"/>
-            </a:solidFill>
             <a:ln w="20160">
               <a:solidFill>
-                <a:srgbClr val="ff6b35"/>
+                <a:srgbClr val="FF6B35"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -918,15 +910,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -934,8 +934,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -999,7 +1000,7 @@
                   <c:v>21.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18.9</c:v>
+                  <c:v>18.899999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>16.5</c:v>
@@ -1026,13 +1027,18 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8EAB-470C-98F1-B3C1E208290E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sprint 2 Burndown'!C3</c:f>
+              <c:f>'Sprint 2 Burndown'!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1042,12 +1048,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="2e86ab"/>
-            </a:solidFill>
             <a:ln w="24840">
               <a:solidFill>
-                <a:srgbClr val="2e86ab"/>
+                <a:srgbClr val="2E86AB"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1056,15 +1059,23 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1072,8 +1083,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1164,7 +1176,20 @@
             </c:numRef>
           </c:val>
           <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8EAB-470C-98F1-B3C1E208290E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1172,7 +1197,7 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:marker val="0"/>
+        <c:smooth val="0"/>
         <c:axId val="67021173"/>
         <c:axId val="81087288"/>
       </c:lineChart>
@@ -1190,7 +1215,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1198,7 +1223,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1234,13 +1259,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="81087288"/>
@@ -1276,7 +1302,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1284,7 +1310,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1320,13 +1346,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="67021173"/>
@@ -1354,35 +1381,42 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -1396,14 +1430,20 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>86400</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3994920" y="504720"/>
-        <a:ext cx="7919640" cy="5039640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1417,7 +1457,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -1431,14 +1471,20 @@
       <xdr:row>28</xdr:row>
       <xdr:rowOff>86400</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3994920" y="504720"/>
-        <a:ext cx="7919640" cy="5039640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1452,41 +1498,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1494,12 +1540,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1528,7 +1574,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1549,7 +1595,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1600,7 +1646,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1618,34 +1664,34 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1656,102 +1702,102 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="3">
         <v>32</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="4">
         <v>28.4</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4">
         <v>25</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="3">
         <v>24.9</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="3">
         <v>20</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="4">
         <v>21.3</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="3">
         <v>17.8</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="4">
         <v>14.2</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="3">
         <v>10.7</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="4">
         <v>7.1</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="3">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1759,37 +1805,29 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1800,124 +1838,124 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="3">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="3">
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="4">
         <v>23.6</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4">
         <v>14</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="3">
         <v>21.3</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="3">
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B7" s="4">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="C7" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="3">
         <v>16.5</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="4">
         <v>14.2</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="3">
         <v>11.8</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="4">
         <v>9.5</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="3">
         <v>7.1</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="4">
         <v>4.7</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="3">
         <v>0</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1925,13 +1963,8 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>